--- a/services/folha/__tests__/fixtures/FASTWELD_-_0109.xlsx
+++ b/services/folha/__tests__/fixtures/FASTWELD_-_0109.xlsx
@@ -63,7 +63,7 @@
     <t>000109</t>
   </si>
   <si>
-    <t>ALEXANDRE ARAUJO DOS SANTOS</t>
+    <t>FUNCIONARIO FICTICIO 01</t>
   </si>
   <si>
     <t>FALTAS (DIAS)</t>
@@ -99,13 +99,13 @@
     <t>000107</t>
   </si>
   <si>
-    <t>ANTONIO SOUZA EVARISTO</t>
+    <t>FUNCIONARIO FICTICIO 02</t>
   </si>
   <si>
     <t>000019</t>
   </si>
   <si>
-    <t>ARNEZILDO REINALDO DE SOUSA</t>
+    <t>FUNCIONARIO FICTICIO 03</t>
   </si>
   <si>
     <t>0001</t>
@@ -117,13 +117,13 @@
     <t>000137</t>
   </si>
   <si>
-    <t>CARLOS ALBERTO DA SILVA</t>
+    <t>FUNCIONARIO FICTICIO 04</t>
   </si>
   <si>
     <t>000125</t>
   </si>
   <si>
-    <t>CARLOS RODRIGUES VIANA DOS SANTO</t>
+    <t>FUNCIONARIO FICTICIO 05</t>
   </si>
   <si>
     <t>CONTRIBUIÇÃO ASSISTENCIAL</t>
@@ -132,79 +132,79 @@
     <t>000152</t>
   </si>
   <si>
-    <t>EDUARDO ALVES AMBROSIO</t>
+    <t>FUNCIONARIO FICTICIO 06</t>
   </si>
   <si>
     <t>000120</t>
   </si>
   <si>
-    <t>ELOETE CRISTIANE RAMOS CARDOSO</t>
+    <t>FUNCIONARIO FICTICIO 07</t>
   </si>
   <si>
     <t>000148</t>
   </si>
   <si>
-    <t>JOHNATA ADRIANO DA SILVA</t>
+    <t>FUNCIONARIO FICTICIO 08</t>
   </si>
   <si>
     <t>000142</t>
   </si>
   <si>
-    <t>JOSE FELIPE DE ARRUDA SILVA</t>
+    <t>FUNCIONARIO FICTICIO 09</t>
   </si>
   <si>
     <t>000016</t>
   </si>
   <si>
-    <t>JOSE LUIZ DOS SANTOS SAMPAIO</t>
+    <t>FUNCIONARIO FICTICIO 10</t>
   </si>
   <si>
     <t>000055</t>
   </si>
   <si>
-    <t>JOSI SANTOS DE AZEVEDO FINARDI</t>
+    <t>FUNCIONARIO FICTICIO 11</t>
   </si>
   <si>
     <t>000138</t>
   </si>
   <si>
-    <t>LANA XAVIER DE MOURA</t>
+    <t>FUNCIONARIO FICTICIO 12</t>
   </si>
   <si>
     <t>000086</t>
   </si>
   <si>
-    <t>LEANDRO HELENO COSTA DE ALBUQUE</t>
+    <t>FUNCIONARIO FICTICIO 13</t>
   </si>
   <si>
     <t>000136</t>
   </si>
   <si>
-    <t>MARIA JOSE GOMES DE OLIVEIRA</t>
+    <t>FUNCIONARIO FICTICIO 14</t>
   </si>
   <si>
     <t>000112</t>
   </si>
   <si>
-    <t>MASTERSON DE MATOS</t>
+    <t>FUNCIONARIO FICTICIO 15</t>
   </si>
   <si>
     <t>000154</t>
   </si>
   <si>
-    <t>PAULO FERNANDES BALAN</t>
+    <t>FUNCIONARIO FICTICIO 16</t>
   </si>
   <si>
     <t>000098</t>
   </si>
   <si>
-    <t>SONIA CRISTINA SILVA</t>
+    <t>FUNCIONARIO FICTICIO 17</t>
   </si>
   <si>
     <t>000132</t>
   </si>
   <si>
-    <t>VANDERLANDO CONCEIÇÃO SILVA</t>
+    <t>FUNCIONARIO FICTICIO 18</t>
   </si>
   <si>
     <t>PENSÃO ALIMENTÍCIA</t>
@@ -213,7 +213,7 @@
     <t>000036</t>
   </si>
   <si>
-    <t>VINICIUS MEDEIROS BOTELHO</t>
+    <t>FUNCIONARIO FICTICIO 19</t>
   </si>
 </sst>
 </file>

--- a/services/folha/__tests__/fixtures/FASTWELD_-_0109.xlsx
+++ b/services/folha/__tests__/fixtures/FASTWELD_-_0109.xlsx
@@ -63,7 +63,7 @@
     <t>000109</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 01</t>
+    <t>ALEXANDRE ARAUJO DOS SANTOS</t>
   </si>
   <si>
     <t>FALTAS (DIAS)</t>
@@ -99,13 +99,13 @@
     <t>000107</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 02</t>
+    <t>ANTONIO SOUZA EVARISTO</t>
   </si>
   <si>
     <t>000019</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 03</t>
+    <t>ARNEZILDO REINALDO DE SOUSA</t>
   </si>
   <si>
     <t>0001</t>
@@ -117,13 +117,13 @@
     <t>000137</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 04</t>
+    <t>CARLOS ALBERTO DA SILVA</t>
   </si>
   <si>
     <t>000125</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 05</t>
+    <t>CARLOS RODRIGUES VIANA DOS SANTO</t>
   </si>
   <si>
     <t>CONTRIBUIÇÃO ASSISTENCIAL</t>
@@ -132,79 +132,79 @@
     <t>000152</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 06</t>
+    <t>EDUARDO ALVES AMBROSIO</t>
   </si>
   <si>
     <t>000120</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 07</t>
+    <t>ELOETE CRISTIANE RAMOS CARDOSO</t>
   </si>
   <si>
     <t>000148</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 08</t>
+    <t>JOHNATA ADRIANO DA SILVA</t>
   </si>
   <si>
     <t>000142</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 09</t>
+    <t>JOSE FELIPE DE ARRUDA SILVA</t>
   </si>
   <si>
     <t>000016</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 10</t>
+    <t>JOSE LUIZ DOS SANTOS SAMPAIO</t>
   </si>
   <si>
     <t>000055</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 11</t>
+    <t>JOSI SANTOS DE AZEVEDO FINARDI</t>
   </si>
   <si>
     <t>000138</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 12</t>
+    <t>LANA XAVIER DE MOURA</t>
   </si>
   <si>
     <t>000086</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 13</t>
+    <t>LEANDRO HELENO COSTA DE ALBUQUE</t>
   </si>
   <si>
     <t>000136</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 14</t>
+    <t>MARIA JOSE GOMES DE OLIVEIRA</t>
   </si>
   <si>
     <t>000112</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 15</t>
+    <t>MASTERSON DE MATOS</t>
   </si>
   <si>
     <t>000154</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 16</t>
+    <t>PAULO FERNANDES BALAN</t>
   </si>
   <si>
     <t>000098</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 17</t>
+    <t>SONIA CRISTINA SILVA</t>
   </si>
   <si>
     <t>000132</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 18</t>
+    <t>VANDERLANDO CONCEIÇÃO SILVA</t>
   </si>
   <si>
     <t>PENSÃO ALIMENTÍCIA</t>
@@ -213,7 +213,7 @@
     <t>000036</t>
   </si>
   <si>
-    <t>FUNCIONARIO FICTICIO 19</t>
+    <t>VINICIUS MEDEIROS BOTELHO</t>
   </si>
 </sst>
 </file>
